--- a/AAII_Financials/Yearly/ARW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ARW_YR_FIN.xlsx
@@ -1010,13 +1010,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-11600</v>
+        <v>-10200</v>
       </c>
       <c r="E14" s="3">
-        <v>198200</v>
+        <v>113700</v>
       </c>
       <c r="F14" s="3">
-        <v>-24100</v>
+        <v>-43200</v>
       </c>
       <c r="G14" s="3">
         <v>12600</v>
@@ -1130,13 +1130,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>29934700</v>
+        <v>29933300</v>
       </c>
       <c r="E17" s="3">
-        <v>26967300</v>
+        <v>27051800</v>
       </c>
       <c r="F17" s="3">
-        <v>31644600</v>
+        <v>31663700</v>
       </c>
       <c r="G17" s="3">
         <v>35049600</v>
@@ -1181,13 +1181,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>918200</v>
+        <v>919600</v>
       </c>
       <c r="E18" s="3">
-        <v>956000</v>
+        <v>871500</v>
       </c>
       <c r="F18" s="3">
-        <v>1462500</v>
+        <v>1443500</v>
       </c>
       <c r="G18" s="3">
         <v>2074800</v>
@@ -1304,13 +1304,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1007300</v>
+        <v>1008700</v>
       </c>
       <c r="E21" s="3">
-        <v>1049600</v>
+        <v>965000</v>
       </c>
       <c r="F21" s="3">
-        <v>1595400</v>
+        <v>1576400</v>
       </c>
       <c r="G21" s="3">
         <v>2259800</v>
